--- a/artfynd/A 16681-2025 artfynd.xlsx
+++ b/artfynd/A 16681-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128499973</v>
+        <v>128500502</v>
       </c>
       <c r="B3" t="n">
-        <v>92387</v>
+        <v>82942</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372847</v>
+        <v>372244</v>
       </c>
       <c r="R3" t="n">
-        <v>7026632</v>
+        <v>7026761</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128500502</v>
+        <v>128499973</v>
       </c>
       <c r="B4" t="n">
-        <v>82942</v>
+        <v>92387</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372244</v>
+        <v>372847</v>
       </c>
       <c r="R4" t="n">
-        <v>7026761</v>
+        <v>7026632</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128499707</v>
+        <v>128499821</v>
       </c>
       <c r="B5" t="n">
-        <v>75171</v>
+        <v>88709</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>4405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Harån, Harån, Jmt</t>
+          <t>Grossmyren, Grossmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>373040</v>
+        <v>372927</v>
       </c>
       <c r="R5" t="n">
-        <v>7026555</v>
+        <v>7026598</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,6 +1057,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1073,45 +1078,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499821</v>
+        <v>128499707</v>
       </c>
       <c r="B6" t="n">
-        <v>88709</v>
+        <v>75171</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4405</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grossmyren, Grossmyren, Jmt</t>
+          <t>Harån, Harån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372927</v>
+        <v>373040</v>
       </c>
       <c r="R6" t="n">
-        <v>7026598</v>
+        <v>7026555</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,11 +1159,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">

--- a/artfynd/A 16681-2025 artfynd.xlsx
+++ b/artfynd/A 16681-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128499765</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128500502</v>
       </c>
       <c r="B3" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128499973</v>
       </c>
       <c r="B4" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128499821</v>
       </c>
       <c r="B5" t="n">
-        <v>88709</v>
+        <v>88715</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>128499707</v>
       </c>
       <c r="B6" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>128500552</v>
       </c>
       <c r="B7" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128499872</v>
       </c>
       <c r="B8" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>128499899</v>
       </c>
       <c r="B9" t="n">
-        <v>78443</v>
+        <v>78447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128500052</v>
       </c>
       <c r="B10" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 16681-2025 artfynd.xlsx
+++ b/artfynd/A 16681-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128500502</v>
+        <v>128499973</v>
       </c>
       <c r="B3" t="n">
-        <v>82946</v>
+        <v>92399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372244</v>
+        <v>372847</v>
       </c>
       <c r="R3" t="n">
-        <v>7026761</v>
+        <v>7026632</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128499973</v>
+        <v>128500502</v>
       </c>
       <c r="B4" t="n">
-        <v>92393</v>
+        <v>82946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372847</v>
+        <v>372244</v>
       </c>
       <c r="R4" t="n">
-        <v>7026632</v>
+        <v>7026761</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
         <v>128499821</v>
       </c>
       <c r="B5" t="n">
-        <v>88715</v>
+        <v>88721</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128499872</v>
       </c>
       <c r="B8" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128500052</v>
       </c>
       <c r="B10" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 16681-2025 artfynd.xlsx
+++ b/artfynd/A 16681-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128499765</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128499973</v>
       </c>
       <c r="B3" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128500502</v>
       </c>
       <c r="B4" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128499821</v>
       </c>
       <c r="B5" t="n">
-        <v>88721</v>
+        <v>88723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>128499707</v>
       </c>
       <c r="B6" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>128500552</v>
       </c>
       <c r="B7" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128499872</v>
       </c>
       <c r="B8" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>128499899</v>
       </c>
       <c r="B9" t="n">
-        <v>78447</v>
+        <v>78449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128500052</v>
       </c>
       <c r="B10" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 16681-2025 artfynd.xlsx
+++ b/artfynd/A 16681-2025 artfynd.xlsx
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128499821</v>
+        <v>128499707</v>
       </c>
       <c r="B5" t="n">
-        <v>88723</v>
+        <v>75177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4405</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grossmyren, Grossmyren, Jmt</t>
+          <t>Harån, Harån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372927</v>
+        <v>373040</v>
       </c>
       <c r="R5" t="n">
-        <v>7026598</v>
+        <v>7026555</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1057,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1078,45 +1073,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499707</v>
+        <v>128499821</v>
       </c>
       <c r="B6" t="n">
-        <v>75177</v>
+        <v>88723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>4405</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Harån, Harån, Jmt</t>
+          <t>Grossmyren, Grossmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>373040</v>
+        <v>372927</v>
       </c>
       <c r="R6" t="n">
-        <v>7026555</v>
+        <v>7026598</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,6 +1154,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">

--- a/artfynd/A 16681-2025 artfynd.xlsx
+++ b/artfynd/A 16681-2025 artfynd.xlsx
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128499707</v>
+        <v>128499821</v>
       </c>
       <c r="B5" t="n">
-        <v>75177</v>
+        <v>88723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>4405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Harån, Harån, Jmt</t>
+          <t>Grossmyren, Grossmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>373040</v>
+        <v>372927</v>
       </c>
       <c r="R5" t="n">
-        <v>7026555</v>
+        <v>7026598</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,6 +1057,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1073,45 +1078,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499821</v>
+        <v>128499707</v>
       </c>
       <c r="B6" t="n">
-        <v>88723</v>
+        <v>75177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4405</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grossmyren, Grossmyren, Jmt</t>
+          <t>Harån, Harån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372927</v>
+        <v>373040</v>
       </c>
       <c r="R6" t="n">
-        <v>7026598</v>
+        <v>7026555</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,11 +1159,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">

--- a/artfynd/A 16681-2025 artfynd.xlsx
+++ b/artfynd/A 16681-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128499973</v>
+        <v>128500502</v>
       </c>
       <c r="B3" t="n">
-        <v>92401</v>
+        <v>82948</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372847</v>
+        <v>372244</v>
       </c>
       <c r="R3" t="n">
-        <v>7026632</v>
+        <v>7026761</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128500502</v>
+        <v>128499973</v>
       </c>
       <c r="B4" t="n">
-        <v>82948</v>
+        <v>92402</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372244</v>
+        <v>372847</v>
       </c>
       <c r="R4" t="n">
-        <v>7026761</v>
+        <v>7026632</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128499821</v>
+        <v>128499707</v>
       </c>
       <c r="B5" t="n">
-        <v>88723</v>
+        <v>75177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4405</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grossmyren, Grossmyren, Jmt</t>
+          <t>Harån, Harån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372927</v>
+        <v>373040</v>
       </c>
       <c r="R5" t="n">
-        <v>7026598</v>
+        <v>7026555</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1057,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1078,45 +1073,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499707</v>
+        <v>128499821</v>
       </c>
       <c r="B6" t="n">
-        <v>75177</v>
+        <v>88723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>4405</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Harån, Harån, Jmt</t>
+          <t>Grossmyren, Grossmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>373040</v>
+        <v>372927</v>
       </c>
       <c r="R6" t="n">
-        <v>7026555</v>
+        <v>7026598</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,6 +1154,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1280,7 +1280,7 @@
         <v>128499872</v>
       </c>
       <c r="B8" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128500052</v>
       </c>
       <c r="B10" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 16681-2025 artfynd.xlsx
+++ b/artfynd/A 16681-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128499765</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128500502</v>
       </c>
       <c r="B3" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128499973</v>
       </c>
       <c r="B4" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128499707</v>
+        <v>128499821</v>
       </c>
       <c r="B5" t="n">
-        <v>75177</v>
+        <v>88750</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>4405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Harån, Harån, Jmt</t>
+          <t>Grossmyren, Grossmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>373040</v>
+        <v>372927</v>
       </c>
       <c r="R5" t="n">
-        <v>7026555</v>
+        <v>7026598</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,6 +1057,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1073,45 +1078,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499821</v>
+        <v>128499707</v>
       </c>
       <c r="B6" t="n">
-        <v>88723</v>
+        <v>75204</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4405</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grossmyren, Grossmyren, Jmt</t>
+          <t>Harån, Harån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372927</v>
+        <v>373040</v>
       </c>
       <c r="R6" t="n">
-        <v>7026598</v>
+        <v>7026555</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,11 +1159,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1178,7 +1178,7 @@
         <v>128500552</v>
       </c>
       <c r="B7" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128499872</v>
       </c>
       <c r="B8" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>128499899</v>
       </c>
       <c r="B9" t="n">
-        <v>78449</v>
+        <v>78476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128500052</v>
       </c>
       <c r="B10" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 16681-2025 artfynd.xlsx
+++ b/artfynd/A 16681-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128499765</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128500502</v>
       </c>
       <c r="B3" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128499973</v>
       </c>
       <c r="B4" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128499821</v>
+        <v>128499707</v>
       </c>
       <c r="B5" t="n">
-        <v>88750</v>
+        <v>75205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4405</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grossmyren, Grossmyren, Jmt</t>
+          <t>Harån, Harån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372927</v>
+        <v>373040</v>
       </c>
       <c r="R5" t="n">
-        <v>7026598</v>
+        <v>7026555</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1057,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1078,45 +1073,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499707</v>
+        <v>128499821</v>
       </c>
       <c r="B6" t="n">
-        <v>75204</v>
+        <v>88754</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>4405</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Harån, Harån, Jmt</t>
+          <t>Grossmyren, Grossmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>373040</v>
+        <v>372927</v>
       </c>
       <c r="R6" t="n">
-        <v>7026555</v>
+        <v>7026598</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,6 +1154,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1178,7 +1178,7 @@
         <v>128500552</v>
       </c>
       <c r="B7" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128499872</v>
       </c>
       <c r="B8" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>128499899</v>
       </c>
       <c r="B9" t="n">
-        <v>78476</v>
+        <v>78480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128500052</v>
       </c>
       <c r="B10" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 16681-2025 artfynd.xlsx
+++ b/artfynd/A 16681-2025 artfynd.xlsx
@@ -877,7 +877,7 @@
         <v>128499973</v>
       </c>
       <c r="B4" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128499707</v>
+        <v>128499821</v>
       </c>
       <c r="B5" t="n">
-        <v>75205</v>
+        <v>88755</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>4405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Harån, Harån, Jmt</t>
+          <t>Grossmyren, Grossmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>373040</v>
+        <v>372927</v>
       </c>
       <c r="R5" t="n">
-        <v>7026555</v>
+        <v>7026598</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,6 +1057,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1073,45 +1078,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499821</v>
+        <v>128499707</v>
       </c>
       <c r="B6" t="n">
-        <v>88754</v>
+        <v>75205</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4405</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grossmyren, Grossmyren, Jmt</t>
+          <t>Harån, Harån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372927</v>
+        <v>373040</v>
       </c>
       <c r="R6" t="n">
-        <v>7026598</v>
+        <v>7026555</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,11 +1159,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1280,7 +1280,7 @@
         <v>128499872</v>
       </c>
       <c r="B8" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128500052</v>
       </c>
       <c r="B10" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 16681-2025 artfynd.xlsx
+++ b/artfynd/A 16681-2025 artfynd.xlsx
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128499821</v>
+        <v>128499707</v>
       </c>
       <c r="B5" t="n">
-        <v>88755</v>
+        <v>75205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4405</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grossmyren, Grossmyren, Jmt</t>
+          <t>Harån, Harån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372927</v>
+        <v>373040</v>
       </c>
       <c r="R5" t="n">
-        <v>7026598</v>
+        <v>7026555</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1057,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1078,45 +1073,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499707</v>
+        <v>128499821</v>
       </c>
       <c r="B6" t="n">
-        <v>75205</v>
+        <v>88755</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>4405</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Harån, Harån, Jmt</t>
+          <t>Grossmyren, Grossmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>373040</v>
+        <v>372927</v>
       </c>
       <c r="R6" t="n">
-        <v>7026555</v>
+        <v>7026598</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,6 +1154,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">

--- a/artfynd/A 16681-2025 artfynd.xlsx
+++ b/artfynd/A 16681-2025 artfynd.xlsx
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128499707</v>
+        <v>128499821</v>
       </c>
       <c r="B5" t="n">
-        <v>75205</v>
+        <v>88755</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>4405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Harån, Harån, Jmt</t>
+          <t>Grossmyren, Grossmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>373040</v>
+        <v>372927</v>
       </c>
       <c r="R5" t="n">
-        <v>7026555</v>
+        <v>7026598</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,6 +1057,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1073,45 +1078,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499821</v>
+        <v>128499707</v>
       </c>
       <c r="B6" t="n">
-        <v>88755</v>
+        <v>75205</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4405</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grossmyren, Grossmyren, Jmt</t>
+          <t>Harån, Harån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372927</v>
+        <v>373040</v>
       </c>
       <c r="R6" t="n">
-        <v>7026598</v>
+        <v>7026555</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,11 +1159,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">

--- a/artfynd/A 16681-2025 artfynd.xlsx
+++ b/artfynd/A 16681-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128499765</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128500502</v>
       </c>
       <c r="B3" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128499973</v>
       </c>
       <c r="B4" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128499821</v>
       </c>
       <c r="B5" t="n">
-        <v>88755</v>
+        <v>88759</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>128499707</v>
       </c>
       <c r="B6" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>128500552</v>
       </c>
       <c r="B7" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128499872</v>
       </c>
       <c r="B8" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>128499899</v>
       </c>
       <c r="B9" t="n">
-        <v>78480</v>
+        <v>78484</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128500052</v>
       </c>
       <c r="B10" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 16681-2025 artfynd.xlsx
+++ b/artfynd/A 16681-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128500502</v>
+        <v>128499973</v>
       </c>
       <c r="B3" t="n">
-        <v>82983</v>
+        <v>92443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372244</v>
+        <v>372847</v>
       </c>
       <c r="R3" t="n">
-        <v>7026761</v>
+        <v>7026632</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128499973</v>
+        <v>128500502</v>
       </c>
       <c r="B4" t="n">
-        <v>92443</v>
+        <v>82983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372847</v>
+        <v>372244</v>
       </c>
       <c r="R4" t="n">
-        <v>7026632</v>
+        <v>7026761</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128499821</v>
+        <v>128499707</v>
       </c>
       <c r="B5" t="n">
-        <v>88759</v>
+        <v>75209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4405</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grossmyren, Grossmyren, Jmt</t>
+          <t>Harån, Harån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372927</v>
+        <v>373040</v>
       </c>
       <c r="R5" t="n">
-        <v>7026598</v>
+        <v>7026555</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1057,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1078,45 +1073,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499707</v>
+        <v>128499821</v>
       </c>
       <c r="B6" t="n">
-        <v>75209</v>
+        <v>88759</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>4405</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Harån, Harån, Jmt</t>
+          <t>Grossmyren, Grossmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>373040</v>
+        <v>372927</v>
       </c>
       <c r="R6" t="n">
-        <v>7026555</v>
+        <v>7026598</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,6 +1154,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">

--- a/artfynd/A 16681-2025 artfynd.xlsx
+++ b/artfynd/A 16681-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128499765</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128499973</v>
+        <v>128500502</v>
       </c>
       <c r="B3" t="n">
-        <v>92443</v>
+        <v>82892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372847</v>
+        <v>372244</v>
       </c>
       <c r="R3" t="n">
-        <v>7026632</v>
+        <v>7026761</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128500502</v>
+        <v>128499973</v>
       </c>
       <c r="B4" t="n">
-        <v>82983</v>
+        <v>92448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372244</v>
+        <v>372847</v>
       </c>
       <c r="R4" t="n">
-        <v>7026761</v>
+        <v>7026632</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128499707</v>
+        <v>128499821</v>
       </c>
       <c r="B5" t="n">
-        <v>75209</v>
+        <v>88764</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>4405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Harån, Harån, Jmt</t>
+          <t>Grossmyren, Grossmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>373040</v>
+        <v>372927</v>
       </c>
       <c r="R5" t="n">
-        <v>7026555</v>
+        <v>7026598</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,6 +1057,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1073,45 +1078,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499821</v>
+        <v>128499707</v>
       </c>
       <c r="B6" t="n">
-        <v>88759</v>
+        <v>83005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4405</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grossmyren, Grossmyren, Jmt</t>
+          <t>Harån, Harån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372927</v>
+        <v>373040</v>
       </c>
       <c r="R6" t="n">
-        <v>7026598</v>
+        <v>7026555</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,11 +1159,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1178,7 +1178,7 @@
         <v>128500552</v>
       </c>
       <c r="B7" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128499872</v>
       </c>
       <c r="B8" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>128499899</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
+        <v>78389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128500052</v>
       </c>
       <c r="B10" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 16681-2025 artfynd.xlsx
+++ b/artfynd/A 16681-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128499765</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128500502</v>
       </c>
       <c r="B3" t="n">
-        <v>82892</v>
+        <v>82897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128499973</v>
       </c>
       <c r="B4" t="n">
-        <v>92451</v>
+        <v>92456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128499821</v>
       </c>
       <c r="B5" t="n">
-        <v>88766</v>
+        <v>88771</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>128499707</v>
       </c>
       <c r="B6" t="n">
-        <v>83005</v>
+        <v>83010</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>128500552</v>
       </c>
       <c r="B7" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>128499872</v>
       </c>
       <c r="B8" t="n">
-        <v>91533</v>
+        <v>91538</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>128499899</v>
       </c>
       <c r="B9" t="n">
-        <v>78389</v>
+        <v>78394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128500052</v>
       </c>
       <c r="B10" t="n">
-        <v>91533</v>
+        <v>91538</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 16681-2025 artfynd.xlsx
+++ b/artfynd/A 16681-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128499765</v>
+        <v>128499899</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>78686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Harån, Harån, Jmt</t>
+          <t>Grossmyren, Grossmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372941</v>
+        <v>372874</v>
       </c>
       <c r="R2" t="n">
-        <v>7026588</v>
+        <v>7026621</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,6 +756,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -775,7 +780,7 @@
         <v>128500502</v>
       </c>
       <c r="B3" t="n">
-        <v>82897</v>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128499973</v>
+        <v>128500552</v>
       </c>
       <c r="B4" t="n">
-        <v>92456</v>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372847</v>
+        <v>372209</v>
       </c>
       <c r="R4" t="n">
-        <v>7026632</v>
+        <v>7026747</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
         <v>128499821</v>
       </c>
       <c r="B5" t="n">
-        <v>88771</v>
+        <v>89143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,45 +1083,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499707</v>
+        <v>128499973</v>
       </c>
       <c r="B6" t="n">
-        <v>83010</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Harån, Harån, Jmt</t>
+          <t>Grossmyren, Grossmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>373040</v>
+        <v>372847</v>
       </c>
       <c r="R6" t="n">
-        <v>7026555</v>
+        <v>7026632</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,6 +1164,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1175,45 +1185,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128500552</v>
+        <v>128499765</v>
       </c>
       <c r="B7" t="n">
-        <v>80140</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grossmyren, Grossmyren, Jmt</t>
+          <t>Harån, Harån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372209</v>
+        <v>372941</v>
       </c>
       <c r="R7" t="n">
-        <v>7026747</v>
+        <v>7026588</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,11 +1266,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1277,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128499872</v>
+        <v>128499707</v>
       </c>
       <c r="B8" t="n">
-        <v>91538</v>
+        <v>83307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,34 +1293,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grossmyren, Grossmyren, Jmt</t>
+          <t>Harån, Harån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372901</v>
+        <v>373040</v>
       </c>
       <c r="R8" t="n">
-        <v>7026611</v>
+        <v>7026555</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,11 +1364,6 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1376,210 +1376,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>128499899</v>
-      </c>
-      <c r="B9" t="n">
-        <v>78394</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>498</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Liten sotlav</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Acolium karelicum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Grossmyren, Grossmyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>372874</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7026621</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>128500052</v>
-      </c>
-      <c r="B10" t="n">
-        <v>91538</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Grossmyren, Grossmyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>372712</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7026630</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Gles och lövrik grannaturskog i skog-myrmosaik</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16681-2025 artfynd.xlsx
+++ b/artfynd/A 16681-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128500502</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128500552</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128499899</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128499821</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128499973</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128499765</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,8 +1411,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128499707</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>